--- a/astro-site/public/dl/food-truck-business-plan/food-truck-startup-checklist.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-startup-checklist.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Inspection of the finished, equipped truck. UK: the council inspects and gives you a Food Hygiene Rating (1-5) in your first months.</t>
+          <t>Inspection of the finished, equipped truck. UK: the council inspects and gives you a Food Hygiene Rating (1-5) in your first months in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required).</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Driver's license class (CDL only if GVWR is 26,001 lb or more)</t>
+          <t>Driver's license class (CDL at 26,001 lb GVWR or more, or for a heavy truck-and-trailer combination)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>A regular license covers most trucks under 26,001 lb GVWR; above that a CDL is required (49 CFR 383).</t>
+          <t>Federal rule (49 CFR 383.91): a CDL is required for a single vehicle rated 26,001 lb GVWR or more, or for a combination rated 26,001 lb or more when the trailer is rated over 10,000 lb (Class A). Below that, most trucks need only a regular license; check with your state DMV, which may add its own rules.</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Tank size is set by your county (in gallons): check with your health department. Gray water usually has to exceed fresh water. The kit's bare minimum is about 10.5 gallons fresh and 16 gray (40 and 60 liters); local rules are often higher.</t>
+          <t>Tank sizes are set by your county: check your county's minimum fresh and gray water tank sizes (in gallons) with the health department before you build. Gray water usually has to exceed fresh water.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="74.75" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Explain to the team how their time records and personal data are handled</t>
+          <t>Tell the team how their time records and personal data are handled</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Hand over the written policy with the hiring paperwork; time-clock and payroll data are personal data, not just a labor requirement</t>
+          <t>There is no single federal rule, but some states protect employee data: if your time clock scans fingerprints or faces, Illinois (BIPA) and a few other states require written notice and consent first. Keep payroll records secure</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Your checklist promises a QR loyalty program that collects contact details: it needs a privacy notice up front, and consent before you send texts.</t>
+          <t>A QR loyalty program collects contact details: post a privacy notice up front, and get consent before you send marketing texts (TCPA).</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/food-truck-business-plan/food-truck-startup-checklist.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-startup-checklist.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Inspection of the finished, equipped truck. UK: the council inspects and gives you a Food Hygiene Rating (1-5) in your first months in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required).</t>
+          <t>Inspection of the finished, equipped truck. UK: the council inspects and gives you a Food Hygiene Rating (0-5) in your first months in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required).</t>
         </is>
       </c>
     </row>
